--- a/data/trans_dic/P19E_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Edad-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,93; 30,95</t>
+          <t>21,71; 30,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,01; 13,05</t>
+          <t>4,91; 13,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,59; 18,66</t>
+          <t>11,63; 18,79</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,18; 13,23</t>
+          <t>5,03; 13,1</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,66; 23,61</t>
+          <t>18,2; 23,66</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,73</t>
+          <t>5,66; 11,51</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>23,99; 31,38</t>
+          <t>24,06; 31,41</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>18,83; 29,41</t>
+          <t>19,19; 29,61</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,7; 20,83</t>
+          <t>14,83; 21,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,98; 9,78</t>
+          <t>4,33; 10,27</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,47; 25,41</t>
+          <t>20,28; 25,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,38; 18,03</t>
+          <t>11,12; 18,2</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>26,03; 33,33</t>
+          <t>25,92; 32,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,1; 24,2</t>
+          <t>17,09; 24,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,45; 21,38</t>
+          <t>14,61; 20,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,78; 13,19</t>
+          <t>8,96; 13,35</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,34; 26,13</t>
+          <t>21,32; 26,0</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,53; 17,84</t>
+          <t>13,44; 17,65</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,63; 39,13</t>
+          <t>31,27; 39,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,45; 27,46</t>
+          <t>7,98; 27,67</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,9; 24,82</t>
+          <t>18,19; 24,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,32; 15,56</t>
+          <t>11,06; 15,9</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,81; 30,83</t>
+          <t>25,69; 30,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,65; 20,36</t>
+          <t>9,82; 20,28</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,98; 44,46</t>
+          <t>34,5; 44,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,63; 35,24</t>
+          <t>27,48; 34,84</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22,74; 31,34</t>
+          <t>23,1; 31,43</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,72; 18,42</t>
+          <t>13,75; 18,57</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,03; 36,19</t>
+          <t>30,0; 36,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,8; 26,17</t>
+          <t>21,64; 26,09</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42,16; 53,55</t>
+          <t>42,53; 54,05</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>29,32; 37,11</t>
+          <t>28,94; 36,83</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,97; 35,59</t>
+          <t>25,43; 35,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,52; 22,86</t>
+          <t>4,53; 22,95</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,21; 42,98</t>
+          <t>35,13; 42,62</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,15; 27,84</t>
+          <t>11,0; 27,93</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,52; 59,27</t>
+          <t>47,14; 59,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,26; 49,28</t>
+          <t>40,53; 49,57</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39,76; 52,33</t>
+          <t>40,44; 52,14</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>38,09; 44,86</t>
+          <t>37,64; 44,39</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,48; 52,81</t>
+          <t>44,98; 53,28</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,83; 45,56</t>
+          <t>39,82; 45,67</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,14; 36,55</t>
+          <t>33,11; 36,54</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,78; 26,57</t>
+          <t>18,67; 26,66</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,56; 25,24</t>
+          <t>22,52; 25,52</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,86; 16,97</t>
+          <t>12,45; 17,0</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,14; 30,32</t>
+          <t>28,07; 30,41</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,03; 21,28</t>
+          <t>17,35; 21,29</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que se cepilla los dientes una o ninguna vez al día</t>
+          <t>Población que se cepilla los dientes una o ninguna vez al día (tasa de respuesta: 98,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>90154; 127231</t>
+          <t>89280; 125108</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20055; 52189</t>
+          <t>19639; 53193</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>44832; 72208</t>
+          <t>45006; 72707</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16209; 41448</t>
+          <t>15763; 41015</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>140946; 188450</t>
+          <t>145266; 188843</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43710; 83621</t>
+          <t>40377; 82059</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>138788; 181522</t>
+          <t>139198; 181706</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79737; 124559</t>
+          <t>81281; 125426</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>81564; 115586</t>
+          <t>82329; 117812</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>20370; 50022</t>
+          <t>22158; 52547</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>232052; 288018</t>
+          <t>229861; 285577</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>106409; 168585</t>
+          <t>103960; 170200</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>171430; 219510</t>
+          <t>170702; 216756</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91706; 129811</t>
+          <t>91666; 129145</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>100494; 139048</t>
+          <t>95046; 135084</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>47610; 71552</t>
+          <t>48569; 72385</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>279274; 341990</t>
+          <t>279128; 340262</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>145915; 192424</t>
+          <t>144980; 190429</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>198911; 246039</t>
+          <t>196666; 248566</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>74738; 242937</t>
+          <t>70605; 244827</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>114745; 159137</t>
+          <t>116625; 159131</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>80556; 110699</t>
+          <t>78667; 113121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>327802; 391572</t>
+          <t>326252; 393265</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>154066; 324971</t>
+          <t>156664; 323754</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>160469; 203931</t>
+          <t>158272; 202310</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>154543; 197144</t>
+          <t>153700; 194875</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>109692; 151148</t>
+          <t>111441; 151592</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74536; 100030</t>
+          <t>74669; 100870</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>282568; 340541</t>
+          <t>282296; 345209</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>240300; 288500</t>
+          <t>238613; 287621</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>135651; 172325</t>
+          <t>136851; 173908</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>107306; 135810</t>
+          <t>105910; 134798</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>93782; 128539</t>
+          <t>91849; 128705</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33401; 138432</t>
+          <t>27451; 138967</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>240481; 293534</t>
+          <t>239941; 291095</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>108332; 270515</t>
+          <t>106903; 271402</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>114247; 142518</t>
+          <t>113342; 142460</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>110918; 135748</t>
+          <t>111643; 136548</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>150622; 198231</t>
+          <t>153193; 197503</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>157600; 185597</t>
+          <t>155749; 183682</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>275426; 327036</t>
+          <t>278529; 329936</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>274499; 313996</t>
+          <t>274428; 314784</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1092862; 1205256</t>
+          <t>1091847; 1204950</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>647156; 915610</t>
+          <t>643385; 918610</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>779455; 872098</t>
+          <t>778291; 881775</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>468059; 617864</t>
+          <t>453223; 618795</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1900490; 2047522</t>
+          <t>1895627; 2053835</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1206988; 1507856</t>
+          <t>1229740; 1508502</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P19E_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P19E_R-Edad-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,92%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>9,63%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>21,71; 30,43</t>
+          <t>21,82; 31,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4,91; 13,3</t>
+          <t>5,79; 14,07</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,63; 18,79</t>
+          <t>11,73; 19,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,03; 13,1</t>
+          <t>6,33; 15,41</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>18,2; 23,66</t>
+          <t>17,9; 23,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,66; 11,51</t>
+          <t>7,06; 13,04</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>24,08%</t>
+          <t>23,9%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>16,22%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,06; 31,41</t>
+          <t>24,18; 31,55</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>19,19; 29,61</t>
+          <t>19,25; 29,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>14,83; 21,23</t>
+          <t>14,63; 20,77</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4,33; 10,27</t>
+          <t>6,44; 11,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,28; 25,19</t>
+          <t>20,03; 25,22</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,12; 18,2</t>
+          <t>13,45; 19,21</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>19,95%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>25,92; 32,91</t>
+          <t>26,26; 33,58</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,09; 24,08</t>
+          <t>16,98; 23,55</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>14,61; 20,77</t>
+          <t>15,16; 21,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8,96; 13,35</t>
+          <t>8,83; 13,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,32; 26,0</t>
+          <t>21,5; 26,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,44; 17,65</t>
+          <t>13,48; 17,6</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,89%</t>
+          <t>24,99%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>14,1%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>19,4%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>31,27; 39,53</t>
+          <t>31,56; 39,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,98; 27,67</t>
+          <t>21,95; 28,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>18,19; 24,82</t>
+          <t>18,72; 24,75</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,06; 15,9</t>
+          <t>11,94; 16,23</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>25,69; 30,97</t>
+          <t>25,79; 30,89</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>9,82; 20,28</t>
+          <t>17,51; 21,49</t>
         </is>
       </c>
     </row>
@@ -919,7 +919,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -929,7 +929,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -939,7 +939,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>22,84%</t>
         </is>
       </c>
     </row>
@@ -952,32 +952,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>34,5; 44,1</t>
+          <t>34,79; 44,58</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>27,48; 34,84</t>
+          <t>26,4; 33,32</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>23,1; 31,43</t>
+          <t>23,05; 31,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>13,75; 18,57</t>
+          <t>13,65; 18,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>30,0; 36,68</t>
+          <t>30,14; 36,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,64; 26,09</t>
+          <t>20,84; 25,15</t>
         </is>
       </c>
     </row>
@@ -999,7 +999,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>31,65%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1009,7 +1009,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14,58%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>26,38%</t>
         </is>
       </c>
     </row>
@@ -1032,32 +1032,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42,53; 54,05</t>
+          <t>42,52; 54,19</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>28,94; 36,83</t>
+          <t>27,81; 35,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25,43; 35,64</t>
+          <t>25,74; 35,6</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4,53; 22,95</t>
+          <t>18,69; 24,07</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,13; 42,62</t>
+          <t>35,34; 42,94</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,0; 27,93</t>
+          <t>24,14; 28,74</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>44,76%</t>
+          <t>43,22%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>41,46%</t>
         </is>
       </c>
     </row>
@@ -1112,32 +1112,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>47,14; 59,25</t>
+          <t>47,68; 59,04</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>40,53; 49,57</t>
+          <t>38,7; 48,09</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>40,44; 52,14</t>
+          <t>40,54; 52,4</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>37,64; 44,39</t>
+          <t>36,79; 43,87</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>44,98; 53,28</t>
+          <t>44,81; 53,19</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,82; 45,67</t>
+          <t>38,83; 44,29</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -1169,7 +1169,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>16,76%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1179,7 +1179,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>20,92%</t>
         </is>
       </c>
     </row>
@@ -1192,32 +1192,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>33,11; 36,54</t>
+          <t>33,07; 36,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,67; 26,66</t>
+          <t>23,71; 26,88</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,52; 25,52</t>
+          <t>22,62; 25,47</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>12,45; 17,0</t>
+          <t>15,74; 17,88</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>28,07; 30,41</t>
+          <t>28,13; 30,36</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,35; 21,29</t>
+          <t>20,02; 21,83</t>
         </is>
       </c>
     </row>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>33667</t>
+          <t>38210</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26456</t>
+          <t>35945</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60124</t>
+          <t>74155</t>
         </is>
       </c>
     </row>
@@ -1425,32 +1425,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>89280; 125108</t>
+          <t>89716; 127515</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>19639; 53193</t>
+          <t>23615; 57374</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>45006; 72707</t>
+          <t>45376; 73753</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15763; 41015</t>
+          <t>22963; 55870</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>145266; 188843</t>
+          <t>142821; 189837</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>40377; 82059</t>
+          <t>54364; 100461</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>101994</t>
+          <t>113973</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36591</t>
+          <t>44610</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>138584</t>
+          <t>158582</t>
         </is>
       </c>
     </row>
@@ -1543,32 +1543,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>139198; 181706</t>
+          <t>139849; 182500</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>81281; 125426</t>
+          <t>91822; 138846</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>82329; 117812</t>
+          <t>81187; 115301</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22158; 52547</t>
+          <t>32290; 57908</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>229861; 285577</t>
+          <t>227056; 285830</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>103960; 170200</t>
+          <t>131512; 187910</t>
         </is>
       </c>
     </row>
@@ -1628,7 +1628,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>109492</t>
+          <t>123848</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>67219</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>168519</t>
+          <t>191067</t>
         </is>
       </c>
     </row>
@@ -1661,32 +1661,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>170702; 216756</t>
+          <t>172952; 221143</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>91666; 129145</t>
+          <t>105405; 146226</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95046; 135084</t>
+          <t>98623; 136687</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48569; 72385</t>
+          <t>54849; 81418</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>279128; 340262</t>
+          <t>281397; 342265</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>144980; 190429</t>
+          <t>167502; 218640</t>
         </is>
       </c>
     </row>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>167083</t>
+          <t>174200</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>96641</t>
+          <t>103642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1766,7 +1766,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>263724</t>
+          <t>277842</t>
         </is>
       </c>
     </row>
@@ -1779,32 +1779,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>196666; 248566</t>
+          <t>198470; 249140</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>70605; 244827</t>
+          <t>153026; 197097</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>116625; 159131</t>
+          <t>119999; 158664</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>78667; 113121</t>
+          <t>87761; 119315</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>326252; 393265</t>
+          <t>327538; 392235</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>156664; 323754</t>
+          <t>250727; 307789</t>
         </is>
       </c>
     </row>
@@ -1864,7 +1864,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>175335</t>
+          <t>181262</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87618</t>
+          <t>95427</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>262954</t>
+          <t>276689</t>
         </is>
       </c>
     </row>
@@ -1897,32 +1897,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>158272; 202310</t>
+          <t>159607; 204506</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>153700; 194875</t>
+          <t>160001; 201970</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>111441; 151592</t>
+          <t>111186; 152871</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>74669; 100870</t>
+          <t>82641; 109490</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>282296; 345209</t>
+          <t>283611; 342953</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>238613; 287621</t>
+          <t>252456; 304635</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>120481</t>
+          <t>128102</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>88286</t>
+          <t>93693</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2002,7 +2002,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>208767</t>
+          <t>221794</t>
         </is>
       </c>
     </row>
@@ -2015,32 +2015,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>136851; 173908</t>
+          <t>136809; 174372</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>105910; 134798</t>
+          <t>112570; 144818</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>91849; 128705</t>
+          <t>92968; 128578</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>27451; 138967</t>
+          <t>81457; 104887</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>239941; 291095</t>
+          <t>241365; 293229</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>106903; 271402</t>
+          <t>202914; 241578</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>123307</t>
+          <t>130425</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>170696</t>
+          <t>181771</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2120,7 +2120,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>294003</t>
+          <t>312196</t>
         </is>
       </c>
     </row>
@@ -2133,32 +2133,32 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>113342; 142460</t>
+          <t>114631; 141947</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>111643; 136548</t>
+          <t>116784; 145097</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>153193; 197503</t>
+          <t>153565; 198507</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>155749; 183682</t>
+          <t>166006; 197917</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>278529; 329936</t>
+          <t>277466; 329376</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>274428; 314784</t>
+          <t>292346; 333483</t>
         </is>
       </c>
     </row>
@@ -2218,7 +2218,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>831359</t>
+          <t>890020</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>565315</t>
+          <t>622307</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -2238,7 +2238,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>1396675</t>
+          <t>1512326</t>
         </is>
       </c>
     </row>
@@ -2251,32 +2251,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>1091847; 1204950</t>
+          <t>1090513; 1200348</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>643385; 918610</t>
+          <t>833545; 944961</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>778291; 881775</t>
+          <t>781514; 880129</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>453223; 618795</t>
+          <t>584212; 663759</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>1895627; 2053835</t>
+          <t>1899530; 2050258</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>1229740; 1508502</t>
+          <t>1447161; 1578159</t>
         </is>
       </c>
     </row>
